--- a/artfynd/A 43860-2025 artfynd.xlsx
+++ b/artfynd/A 43860-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>65787847</v>
       </c>
       <c r="B2" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660879.3496814447</v>
+        <v>660879</v>
       </c>
       <c r="R2" t="n">
-        <v>6705301.112432893</v>
+        <v>6705301</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1995-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1995-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>65785866</v>
       </c>
       <c r="B3" t="n">
-        <v>100560</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660879.3496814447</v>
+        <v>660879</v>
       </c>
       <c r="R3" t="n">
-        <v>6705301.112432893</v>
+        <v>6705301</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -874,19 +854,9 @@
           <t>1995-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1995-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>65769405</v>
       </c>
       <c r="B4" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>660879.3496814447</v>
+        <v>660879</v>
       </c>
       <c r="R4" t="n">
-        <v>6705301.112432893</v>
+        <v>6705301</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1000,19 +965,9 @@
           <t>1995-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1995-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 43860-2025 artfynd.xlsx
+++ b/artfynd/A 43860-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65787847</v>
       </c>
       <c r="B2" t="n">
-        <v>103595</v>
+        <v>103596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>65785866</v>
       </c>
       <c r="B3" t="n">
-        <v>103363</v>
+        <v>103364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>65769405</v>
       </c>
       <c r="B4" t="n">
-        <v>102153</v>
+        <v>102154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43860-2025 artfynd.xlsx
+++ b/artfynd/A 43860-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65787847</v>
       </c>
       <c r="B2" t="n">
-        <v>103596</v>
+        <v>103597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>65785866</v>
       </c>
       <c r="B3" t="n">
-        <v>103364</v>
+        <v>103365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>65769405</v>
       </c>
       <c r="B4" t="n">
-        <v>102154</v>
+        <v>102155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43860-2025 artfynd.xlsx
+++ b/artfynd/A 43860-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65787847</v>
       </c>
       <c r="B2" t="n">
-        <v>103597</v>
+        <v>103598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>65785866</v>
       </c>
       <c r="B3" t="n">
-        <v>103365</v>
+        <v>103366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>65769405</v>
       </c>
       <c r="B4" t="n">
-        <v>102155</v>
+        <v>102157</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43860-2025 artfynd.xlsx
+++ b/artfynd/A 43860-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65787847</v>
       </c>
       <c r="B2" t="n">
-        <v>103598</v>
+        <v>103599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>65785866</v>
       </c>
       <c r="B3" t="n">
-        <v>103366</v>
+        <v>103367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>65769405</v>
       </c>
       <c r="B4" t="n">
-        <v>102157</v>
+        <v>102158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43860-2025 artfynd.xlsx
+++ b/artfynd/A 43860-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65787847</v>
       </c>
       <c r="B2" t="n">
-        <v>103599</v>
+        <v>103605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>65785866</v>
       </c>
       <c r="B3" t="n">
-        <v>103367</v>
+        <v>103373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>65769405</v>
       </c>
       <c r="B4" t="n">
-        <v>102158</v>
+        <v>102164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43860-2025 artfynd.xlsx
+++ b/artfynd/A 43860-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65787847</v>
       </c>
       <c r="B2" t="n">
-        <v>103605</v>
+        <v>103609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>65785866</v>
       </c>
       <c r="B3" t="n">
-        <v>103373</v>
+        <v>103377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>65769405</v>
       </c>
       <c r="B4" t="n">
-        <v>102164</v>
+        <v>102167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43860-2025 artfynd.xlsx
+++ b/artfynd/A 43860-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65787847</v>
       </c>
       <c r="B2" t="n">
-        <v>103609</v>
+        <v>103614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>65785866</v>
       </c>
       <c r="B3" t="n">
-        <v>103377</v>
+        <v>103382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>65769405</v>
       </c>
       <c r="B4" t="n">
-        <v>102167</v>
+        <v>102172</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43860-2025 artfynd.xlsx
+++ b/artfynd/A 43860-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65787847</v>
       </c>
       <c r="B2" t="n">
-        <v>103614</v>
+        <v>103617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>65785866</v>
       </c>
       <c r="B3" t="n">
-        <v>103382</v>
+        <v>103385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>65769405</v>
       </c>
       <c r="B4" t="n">
-        <v>102172</v>
+        <v>102175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
